--- a/data/trans_orig/P79A2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A2_2023-Habitat-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2450</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6837</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>6150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>59,3%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>9453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>14915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14002</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>22099</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10441</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22430</t>
+          <t>28104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>73,57%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12520</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19062</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>24341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9800</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>18548</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17613</t>
+          <t>23235</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>92,38%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8352</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17240</t>
+          <t>27280</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21176</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22689</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16582</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>32179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>55328</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32341</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>8665</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>10085</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23702</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>36713</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>53339</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28118</t>
+          <t>39613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>57488</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30635</t>
+          <t>46715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>65387</t>
+          <t>90492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>88532</t>
+          <t>116904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>16967</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>25785</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>26667</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35686</t>
+          <t>37440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36760</t>
+          <t>43634</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48627</t>
+          <t>59060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47693</t>
+          <t>65398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66321</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
